--- a/results/CB/ResponseCBsCorrected_with_context_fields.xlsx
+++ b/results/CB/ResponseCBsCorrected_with_context_fields.xlsx
@@ -45224,7 +45224,11 @@
       <c r="D1280" t="n">
         <v>2237</v>
       </c>
-      <c r="E1280" t="inlineStr"/>
+      <c r="E1280" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
       <c r="F1280" t="n">
         <v>1279</v>
       </c>
@@ -45317,7 +45321,11 @@
       <c r="D1283" t="n">
         <v>2240</v>
       </c>
-      <c r="E1283" t="inlineStr"/>
+      <c r="E1283" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
       <c r="F1283" t="n">
         <v>1282</v>
       </c>

--- a/results/CB/ResponseCBsCorrected_with_context_fields.xlsx
+++ b/results/CB/ResponseCBsCorrected_with_context_fields.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1736"/>
+  <dimension ref="A1:I1756"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5060,7 +5060,7 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -5200,7 +5200,7 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -5375,7 +5375,7 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -6950,7 +6950,7 @@
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -7020,7 +7020,7 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -7265,7 +7265,7 @@
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -9225,7 +9225,7 @@
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -9330,7 +9330,7 @@
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -9855,7 +9855,7 @@
       </c>
       <c r="I269" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -10065,7 +10065,7 @@
       </c>
       <c r="I275" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -10205,7 +10205,7 @@
       </c>
       <c r="I279" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -10450,7 +10450,7 @@
       </c>
       <c r="I286" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -10765,7 +10765,7 @@
       </c>
       <c r="I295" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -10870,7 +10870,7 @@
       </c>
       <c r="I298" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -10905,7 +10905,7 @@
       </c>
       <c r="I299" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -11080,7 +11080,7 @@
       </c>
       <c r="I304" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -11220,7 +11220,7 @@
       </c>
       <c r="I308" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -11255,7 +11255,7 @@
       </c>
       <c r="I309" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -11955,7 +11955,7 @@
       </c>
       <c r="I329" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -11990,7 +11990,7 @@
       </c>
       <c r="I330" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -12690,7 +12690,7 @@
       </c>
       <c r="I350" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -12830,7 +12830,7 @@
       </c>
       <c r="I354" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -12900,7 +12900,7 @@
       </c>
       <c r="I356" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -17030,7 +17030,7 @@
       </c>
       <c r="I474" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -17065,7 +17065,7 @@
       </c>
       <c r="I475" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -17100,7 +17100,7 @@
       </c>
       <c r="I476" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -17135,7 +17135,7 @@
       </c>
       <c r="I477" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -17345,7 +17345,7 @@
       </c>
       <c r="I483" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -17415,7 +17415,7 @@
       </c>
       <c r="I485" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -20355,7 +20355,7 @@
       </c>
       <c r="I569" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -22525,7 +22525,7 @@
       </c>
       <c r="I631" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -24170,7 +24170,7 @@
       </c>
       <c r="I678" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -24240,7 +24240,7 @@
       </c>
       <c r="I680" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -24520,7 +24520,7 @@
       </c>
       <c r="I688" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -27180,7 +27180,7 @@
       </c>
       <c r="I764" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -27320,7 +27320,7 @@
       </c>
       <c r="I768" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -28020,7 +28020,7 @@
       </c>
       <c r="I788" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -28790,7 +28790,7 @@
       </c>
       <c r="I810" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -29070,7 +29070,7 @@
       </c>
       <c r="I818" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -35860,7 +35860,7 @@
       </c>
       <c r="I1012" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -37050,7 +37050,7 @@
       </c>
       <c r="I1046" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -37295,7 +37295,7 @@
       </c>
       <c r="I1053" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -38205,7 +38205,7 @@
       </c>
       <c r="I1079" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -38240,7 +38240,7 @@
       </c>
       <c r="I1080" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -38275,7 +38275,7 @@
       </c>
       <c r="I1081" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -38310,7 +38310,7 @@
       </c>
       <c r="I1082" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -38345,7 +38345,7 @@
       </c>
       <c r="I1083" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -38380,7 +38380,7 @@
       </c>
       <c r="I1084" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -38415,7 +38415,7 @@
       </c>
       <c r="I1085" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -38450,7 +38450,7 @@
       </c>
       <c r="I1086" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -38485,7 +38485,7 @@
       </c>
       <c r="I1087" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -40900,7 +40900,7 @@
       </c>
       <c r="I1156" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -41600,7 +41600,7 @@
       </c>
       <c r="I1176" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -41635,7 +41635,7 @@
       </c>
       <c r="I1177" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -41670,7 +41670,7 @@
       </c>
       <c r="I1178" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -41705,7 +41705,7 @@
       </c>
       <c r="I1179" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -41740,7 +41740,7 @@
       </c>
       <c r="I1180" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -41775,7 +41775,7 @@
       </c>
       <c r="I1181" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -41810,7 +41810,7 @@
       </c>
       <c r="I1182" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -42405,7 +42405,7 @@
       </c>
       <c r="I1199" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -45240,7 +45240,7 @@
       </c>
       <c r="I1280" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -45271,7 +45271,7 @@
       </c>
       <c r="I1281" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -45302,7 +45302,7 @@
       </c>
       <c r="I1282" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -45337,7 +45337,7 @@
       </c>
       <c r="I1283" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -45368,7 +45368,7 @@
       </c>
       <c r="I1284" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -45403,7 +45403,7 @@
       </c>
       <c r="I1285" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -45438,7 +45438,7 @@
       </c>
       <c r="I1286" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -48623,7 +48623,7 @@
       </c>
       <c r="I1377" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -49918,7 +49918,7 @@
       </c>
       <c r="I1414" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -50058,7 +50058,7 @@
       </c>
       <c r="I1418" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -51493,7 +51493,7 @@
       </c>
       <c r="I1459" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -51866,15 +51866,17 @@
       <c r="F1470" t="n">
         <v>1469</v>
       </c>
-      <c r="G1470" t="n">
-        <v>13.078219</v>
+      <c r="G1470" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
       </c>
       <c r="H1470" s="2" t="n">
         <v>45244.81056145292</v>
       </c>
       <c r="I1470" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime to NULL</t>
         </is>
       </c>
     </row>
@@ -53939,7 +53941,7 @@
       </c>
       <c r="I1529" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -53974,7 +53976,7 @@
       </c>
       <c r="I1530" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -54009,7 +54011,7 @@
       </c>
       <c r="I1531" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -54044,7 +54046,7 @@
       </c>
       <c r="I1532" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -54079,7 +54081,7 @@
       </c>
       <c r="I1533" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -54184,7 +54186,7 @@
       </c>
       <c r="I1536" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -54219,7 +54221,7 @@
       </c>
       <c r="I1537" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -55409,7 +55411,7 @@
       </c>
       <c r="I1571" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -55444,7 +55446,7 @@
       </c>
       <c r="I1572" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -55479,7 +55481,7 @@
       </c>
       <c r="I1573" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -55514,7 +55516,7 @@
       </c>
       <c r="I1574" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -55549,7 +55551,7 @@
       </c>
       <c r="I1575" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -55584,7 +55586,7 @@
       </c>
       <c r="I1576" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -55619,7 +55621,7 @@
       </c>
       <c r="I1577" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -55654,7 +55656,7 @@
       </c>
       <c r="I1578" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -56354,7 +56356,7 @@
       </c>
       <c r="I1598" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -56389,7 +56391,7 @@
       </c>
       <c r="I1599" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -56424,7 +56426,7 @@
       </c>
       <c r="I1600" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -56459,7 +56461,7 @@
       </c>
       <c r="I1601" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -56494,7 +56496,7 @@
       </c>
       <c r="I1602" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -56529,7 +56531,7 @@
       </c>
       <c r="I1603" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -56564,7 +56566,7 @@
       </c>
       <c r="I1604" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -56599,7 +56601,7 @@
       </c>
       <c r="I1605" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -58034,7 +58036,7 @@
       </c>
       <c r="I1646" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -58069,7 +58071,7 @@
       </c>
       <c r="I1647" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -58104,7 +58106,7 @@
       </c>
       <c r="I1648" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -58139,7 +58141,7 @@
       </c>
       <c r="I1649" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -58174,7 +58176,7 @@
       </c>
       <c r="I1650" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -58209,7 +58211,7 @@
       </c>
       <c r="I1651" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -58244,7 +58246,7 @@
       </c>
       <c r="I1652" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -58279,7 +58281,7 @@
       </c>
       <c r="I1653" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -58314,7 +58316,7 @@
       </c>
       <c r="I1654" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -58349,7 +58351,7 @@
       </c>
       <c r="I1655" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -58384,7 +58386,7 @@
       </c>
       <c r="I1656" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -58419,7 +58421,7 @@
       </c>
       <c r="I1657" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -58454,7 +58456,7 @@
       </c>
       <c r="I1658" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -58489,7 +58491,7 @@
       </c>
       <c r="I1659" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -58524,7 +58526,7 @@
       </c>
       <c r="I1660" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -58559,7 +58561,7 @@
       </c>
       <c r="I1661" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -58804,7 +58806,7 @@
       </c>
       <c r="I1668" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -58839,7 +58841,7 @@
       </c>
       <c r="I1669" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -58874,7 +58876,7 @@
       </c>
       <c r="I1670" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -58909,7 +58911,7 @@
       </c>
       <c r="I1671" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -58944,7 +58946,7 @@
       </c>
       <c r="I1672" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -58979,7 +58981,7 @@
       </c>
       <c r="I1673" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -59014,7 +59016,7 @@
       </c>
       <c r="I1674" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -59049,7 +59051,7 @@
       </c>
       <c r="I1675" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -59084,7 +59086,7 @@
       </c>
       <c r="I1676" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -59119,7 +59121,7 @@
       </c>
       <c r="I1677" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -59154,7 +59156,7 @@
       </c>
       <c r="I1678" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -59189,7 +59191,7 @@
       </c>
       <c r="I1679" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -59224,7 +59226,7 @@
       </c>
       <c r="I1680" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -59259,7 +59261,7 @@
       </c>
       <c r="I1681" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -59294,7 +59296,7 @@
       </c>
       <c r="I1682" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -59329,7 +59331,7 @@
       </c>
       <c r="I1683" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -59364,7 +59366,7 @@
       </c>
       <c r="I1684" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -59399,7 +59401,7 @@
       </c>
       <c r="I1685" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -59434,7 +59436,7 @@
       </c>
       <c r="I1686" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -59469,7 +59471,7 @@
       </c>
       <c r="I1687" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -59504,7 +59506,7 @@
       </c>
       <c r="I1688" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -59539,7 +59541,7 @@
       </c>
       <c r="I1689" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -59574,7 +59576,7 @@
       </c>
       <c r="I1690" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -59609,7 +59611,7 @@
       </c>
       <c r="I1691" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -59644,7 +59646,7 @@
       </c>
       <c r="I1692" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -59679,7 +59681,7 @@
       </c>
       <c r="I1693" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -59714,7 +59716,7 @@
       </c>
       <c r="I1694" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -59749,7 +59751,7 @@
       </c>
       <c r="I1695" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -60589,7 +60591,7 @@
       </c>
       <c r="I1719" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -60624,7 +60626,7 @@
       </c>
       <c r="I1720" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -60659,7 +60661,7 @@
       </c>
       <c r="I1721" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -60694,7 +60696,7 @@
       </c>
       <c r="I1722" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -60729,7 +60731,7 @@
       </c>
       <c r="I1723" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -60764,7 +60766,7 @@
       </c>
       <c r="I1724" t="inlineStr">
         <is>
-          <t>Corrected</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -61185,6 +61187,746 @@
       <c r="I1736" t="inlineStr">
         <is>
           <t>Original</t>
+        </is>
+      </c>
+    </row>
+    <row r="1737">
+      <c r="A1737" t="inlineStr">
+        <is>
+          <t>yoshi</t>
+        </is>
+      </c>
+      <c r="B1737" t="n">
+        <v>15</v>
+      </c>
+      <c r="C1737" t="n">
+        <v>184</v>
+      </c>
+      <c r="D1737" t="n">
+        <v>3172</v>
+      </c>
+      <c r="E1737" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="F1737" t="n">
+        <v>3471</v>
+      </c>
+      <c r="G1737" t="n">
+        <v>11.13</v>
+      </c>
+      <c r="H1737" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="I1737" t="inlineStr">
+        <is>
+          <t>Added from Corrections</t>
+        </is>
+      </c>
+    </row>
+    <row r="1738">
+      <c r="A1738" t="inlineStr">
+        <is>
+          <t>yoshi</t>
+        </is>
+      </c>
+      <c r="B1738" t="n">
+        <v>15</v>
+      </c>
+      <c r="C1738" t="n">
+        <v>184</v>
+      </c>
+      <c r="D1738" t="n">
+        <v>3173</v>
+      </c>
+      <c r="E1738" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="F1738" t="n">
+        <v>3472</v>
+      </c>
+      <c r="G1738" t="n">
+        <v>12.67</v>
+      </c>
+      <c r="H1738" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="I1738" t="inlineStr">
+        <is>
+          <t>Added from Corrections</t>
+        </is>
+      </c>
+    </row>
+    <row r="1739">
+      <c r="A1739" t="inlineStr">
+        <is>
+          <t>yoshi</t>
+        </is>
+      </c>
+      <c r="B1739" t="n">
+        <v>15</v>
+      </c>
+      <c r="C1739" t="n">
+        <v>184</v>
+      </c>
+      <c r="D1739" t="n">
+        <v>3174</v>
+      </c>
+      <c r="E1739" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="F1739" t="n">
+        <v>3473</v>
+      </c>
+      <c r="G1739" t="n">
+        <v>11.73</v>
+      </c>
+      <c r="H1739" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="I1739" t="inlineStr">
+        <is>
+          <t>Added from Corrections</t>
+        </is>
+      </c>
+    </row>
+    <row r="1740">
+      <c r="A1740" t="inlineStr">
+        <is>
+          <t>yoshi</t>
+        </is>
+      </c>
+      <c r="B1740" t="n">
+        <v>15</v>
+      </c>
+      <c r="C1740" t="n">
+        <v>184</v>
+      </c>
+      <c r="D1740" t="n">
+        <v>3175</v>
+      </c>
+      <c r="E1740" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="F1740" t="n">
+        <v>3474</v>
+      </c>
+      <c r="G1740" t="n">
+        <v>14</v>
+      </c>
+      <c r="H1740" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="I1740" t="inlineStr">
+        <is>
+          <t>Added from Corrections</t>
+        </is>
+      </c>
+    </row>
+    <row r="1741">
+      <c r="A1741" t="inlineStr">
+        <is>
+          <t>yoshi</t>
+        </is>
+      </c>
+      <c r="B1741" t="n">
+        <v>15</v>
+      </c>
+      <c r="C1741" t="n">
+        <v>184</v>
+      </c>
+      <c r="D1741" t="n">
+        <v>3176</v>
+      </c>
+      <c r="E1741" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="F1741" t="n">
+        <v>3475</v>
+      </c>
+      <c r="G1741" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="H1741" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="I1741" t="inlineStr">
+        <is>
+          <t>Added from Corrections</t>
+        </is>
+      </c>
+    </row>
+    <row r="1742">
+      <c r="A1742" t="inlineStr">
+        <is>
+          <t>yoshi</t>
+        </is>
+      </c>
+      <c r="B1742" t="n">
+        <v>15</v>
+      </c>
+      <c r="C1742" t="n">
+        <v>184</v>
+      </c>
+      <c r="D1742" t="n">
+        <v>3177</v>
+      </c>
+      <c r="E1742" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="F1742" t="n">
+        <v>3476</v>
+      </c>
+      <c r="G1742" t="n">
+        <v>12.94</v>
+      </c>
+      <c r="H1742" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="I1742" t="inlineStr">
+        <is>
+          <t>Added from Corrections</t>
+        </is>
+      </c>
+    </row>
+    <row r="1743">
+      <c r="A1743" t="inlineStr">
+        <is>
+          <t>yoshi</t>
+        </is>
+      </c>
+      <c r="B1743" t="n">
+        <v>15</v>
+      </c>
+      <c r="C1743" t="n">
+        <v>184</v>
+      </c>
+      <c r="D1743" t="n">
+        <v>3178</v>
+      </c>
+      <c r="E1743" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="F1743" t="n">
+        <v>3477</v>
+      </c>
+      <c r="G1743" t="n">
+        <v>12.37</v>
+      </c>
+      <c r="H1743" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="I1743" t="inlineStr">
+        <is>
+          <t>Added from Corrections</t>
+        </is>
+      </c>
+    </row>
+    <row r="1744">
+      <c r="A1744" t="inlineStr">
+        <is>
+          <t>yoshi</t>
+        </is>
+      </c>
+      <c r="B1744" t="n">
+        <v>15</v>
+      </c>
+      <c r="C1744" t="n">
+        <v>184</v>
+      </c>
+      <c r="D1744" t="n">
+        <v>3179</v>
+      </c>
+      <c r="E1744" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="F1744" t="n">
+        <v>3478</v>
+      </c>
+      <c r="G1744" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="H1744" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="I1744" t="inlineStr">
+        <is>
+          <t>Added from Corrections</t>
+        </is>
+      </c>
+    </row>
+    <row r="1745">
+      <c r="A1745" t="inlineStr">
+        <is>
+          <t>yoshi</t>
+        </is>
+      </c>
+      <c r="B1745" t="n">
+        <v>15</v>
+      </c>
+      <c r="C1745" t="n">
+        <v>184</v>
+      </c>
+      <c r="D1745" t="n">
+        <v>3180</v>
+      </c>
+      <c r="E1745" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="F1745" t="n">
+        <v>3479</v>
+      </c>
+      <c r="G1745" t="n">
+        <v>16.89</v>
+      </c>
+      <c r="H1745" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="I1745" t="inlineStr">
+        <is>
+          <t>Added from Corrections</t>
+        </is>
+      </c>
+    </row>
+    <row r="1746">
+      <c r="A1746" t="inlineStr">
+        <is>
+          <t>yoshi</t>
+        </is>
+      </c>
+      <c r="B1746" t="n">
+        <v>15</v>
+      </c>
+      <c r="C1746" t="n">
+        <v>184</v>
+      </c>
+      <c r="D1746" t="n">
+        <v>3181</v>
+      </c>
+      <c r="E1746" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="F1746" t="n">
+        <v>3480</v>
+      </c>
+      <c r="G1746" t="n">
+        <v>11.99</v>
+      </c>
+      <c r="H1746" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="I1746" t="inlineStr">
+        <is>
+          <t>Added from Corrections</t>
+        </is>
+      </c>
+    </row>
+    <row r="1747">
+      <c r="A1747" t="inlineStr">
+        <is>
+          <t>yoshi</t>
+        </is>
+      </c>
+      <c r="B1747" t="n">
+        <v>15</v>
+      </c>
+      <c r="C1747" t="n">
+        <v>184</v>
+      </c>
+      <c r="D1747" t="n">
+        <v>3182</v>
+      </c>
+      <c r="E1747" t="inlineStr">
+        <is>
+          <t>NOGO</t>
+        </is>
+      </c>
+      <c r="F1747" t="n">
+        <v>3481</v>
+      </c>
+      <c r="G1747" t="n">
+        <v>30</v>
+      </c>
+      <c r="H1747" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="I1747" t="inlineStr">
+        <is>
+          <t>Added from Corrections</t>
+        </is>
+      </c>
+    </row>
+    <row r="1748">
+      <c r="A1748" t="inlineStr">
+        <is>
+          <t>yoshi</t>
+        </is>
+      </c>
+      <c r="B1748" t="n">
+        <v>15</v>
+      </c>
+      <c r="C1748" t="n">
+        <v>184</v>
+      </c>
+      <c r="D1748" t="n">
+        <v>3183</v>
+      </c>
+      <c r="E1748" t="inlineStr">
+        <is>
+          <t>NOGO</t>
+        </is>
+      </c>
+      <c r="F1748" t="n">
+        <v>3482</v>
+      </c>
+      <c r="G1748" t="n">
+        <v>30</v>
+      </c>
+      <c r="H1748" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="I1748" t="inlineStr">
+        <is>
+          <t>Added from Corrections</t>
+        </is>
+      </c>
+    </row>
+    <row r="1749">
+      <c r="A1749" t="inlineStr">
+        <is>
+          <t>yoshi</t>
+        </is>
+      </c>
+      <c r="B1749" t="n">
+        <v>15</v>
+      </c>
+      <c r="C1749" t="n">
+        <v>184</v>
+      </c>
+      <c r="D1749" t="n">
+        <v>3184</v>
+      </c>
+      <c r="E1749" t="inlineStr">
+        <is>
+          <t>NOGO</t>
+        </is>
+      </c>
+      <c r="F1749" t="n">
+        <v>3483</v>
+      </c>
+      <c r="G1749" t="n">
+        <v>30</v>
+      </c>
+      <c r="H1749" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="I1749" t="inlineStr">
+        <is>
+          <t>Added from Corrections</t>
+        </is>
+      </c>
+    </row>
+    <row r="1750">
+      <c r="A1750" t="inlineStr">
+        <is>
+          <t>yoshi</t>
+        </is>
+      </c>
+      <c r="B1750" t="n">
+        <v>15</v>
+      </c>
+      <c r="C1750" t="n">
+        <v>184</v>
+      </c>
+      <c r="D1750" t="n">
+        <v>3185</v>
+      </c>
+      <c r="E1750" t="inlineStr">
+        <is>
+          <t>NOGO</t>
+        </is>
+      </c>
+      <c r="F1750" t="n">
+        <v>3484</v>
+      </c>
+      <c r="G1750" t="n">
+        <v>30</v>
+      </c>
+      <c r="H1750" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="I1750" t="inlineStr">
+        <is>
+          <t>Added from Corrections</t>
+        </is>
+      </c>
+    </row>
+    <row r="1751">
+      <c r="A1751" t="inlineStr">
+        <is>
+          <t>yoshi</t>
+        </is>
+      </c>
+      <c r="B1751" t="n">
+        <v>15</v>
+      </c>
+      <c r="C1751" t="n">
+        <v>184</v>
+      </c>
+      <c r="D1751" t="n">
+        <v>3186</v>
+      </c>
+      <c r="E1751" t="inlineStr">
+        <is>
+          <t>NOGO</t>
+        </is>
+      </c>
+      <c r="F1751" t="n">
+        <v>3485</v>
+      </c>
+      <c r="G1751" t="n">
+        <v>30</v>
+      </c>
+      <c r="H1751" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="I1751" t="inlineStr">
+        <is>
+          <t>Added from Corrections</t>
+        </is>
+      </c>
+    </row>
+    <row r="1752">
+      <c r="A1752" t="inlineStr">
+        <is>
+          <t>yoshi</t>
+        </is>
+      </c>
+      <c r="B1752" t="n">
+        <v>15</v>
+      </c>
+      <c r="C1752" t="n">
+        <v>184</v>
+      </c>
+      <c r="D1752" t="n">
+        <v>3187</v>
+      </c>
+      <c r="E1752" t="inlineStr">
+        <is>
+          <t>NOGO</t>
+        </is>
+      </c>
+      <c r="F1752" t="n">
+        <v>3486</v>
+      </c>
+      <c r="G1752" t="n">
+        <v>30</v>
+      </c>
+      <c r="H1752" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="I1752" t="inlineStr">
+        <is>
+          <t>Added from Corrections</t>
+        </is>
+      </c>
+    </row>
+    <row r="1753">
+      <c r="A1753" t="inlineStr">
+        <is>
+          <t>yoshi</t>
+        </is>
+      </c>
+      <c r="B1753" t="n">
+        <v>15</v>
+      </c>
+      <c r="C1753" t="n">
+        <v>184</v>
+      </c>
+      <c r="D1753" t="n">
+        <v>3188</v>
+      </c>
+      <c r="E1753" t="inlineStr">
+        <is>
+          <t>NOGO</t>
+        </is>
+      </c>
+      <c r="F1753" t="n">
+        <v>3487</v>
+      </c>
+      <c r="G1753" t="n">
+        <v>30</v>
+      </c>
+      <c r="H1753" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="I1753" t="inlineStr">
+        <is>
+          <t>Added from Corrections</t>
+        </is>
+      </c>
+    </row>
+    <row r="1754">
+      <c r="A1754" t="inlineStr">
+        <is>
+          <t>yoshi</t>
+        </is>
+      </c>
+      <c r="B1754" t="n">
+        <v>15</v>
+      </c>
+      <c r="C1754" t="n">
+        <v>184</v>
+      </c>
+      <c r="D1754" t="n">
+        <v>3189</v>
+      </c>
+      <c r="E1754" t="inlineStr">
+        <is>
+          <t>NOGO</t>
+        </is>
+      </c>
+      <c r="F1754" t="n">
+        <v>3488</v>
+      </c>
+      <c r="G1754" t="n">
+        <v>30</v>
+      </c>
+      <c r="H1754" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="I1754" t="inlineStr">
+        <is>
+          <t>Added from Corrections</t>
+        </is>
+      </c>
+    </row>
+    <row r="1755">
+      <c r="A1755" t="inlineStr">
+        <is>
+          <t>yoshi</t>
+        </is>
+      </c>
+      <c r="B1755" t="n">
+        <v>15</v>
+      </c>
+      <c r="C1755" t="n">
+        <v>184</v>
+      </c>
+      <c r="D1755" t="n">
+        <v>3190</v>
+      </c>
+      <c r="E1755" t="inlineStr">
+        <is>
+          <t>NOGO</t>
+        </is>
+      </c>
+      <c r="F1755" t="n">
+        <v>3489</v>
+      </c>
+      <c r="G1755" t="n">
+        <v>30</v>
+      </c>
+      <c r="H1755" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="I1755" t="inlineStr">
+        <is>
+          <t>Added from Corrections</t>
+        </is>
+      </c>
+    </row>
+    <row r="1756">
+      <c r="A1756" t="inlineStr">
+        <is>
+          <t>yoshi</t>
+        </is>
+      </c>
+      <c r="B1756" t="n">
+        <v>15</v>
+      </c>
+      <c r="C1756" t="n">
+        <v>184</v>
+      </c>
+      <c r="D1756" t="n">
+        <v>3191</v>
+      </c>
+      <c r="E1756" t="inlineStr">
+        <is>
+          <t>NOGO</t>
+        </is>
+      </c>
+      <c r="F1756" t="n">
+        <v>3490</v>
+      </c>
+      <c r="G1756" t="n">
+        <v>30</v>
+      </c>
+      <c r="H1756" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="I1756" t="inlineStr">
+        <is>
+          <t>Added from Corrections</t>
         </is>
       </c>
     </row>

--- a/results/CB/ResponseCBsCorrected_with_context_fields.xlsx
+++ b/results/CB/ResponseCBsCorrected_with_context_fields.xlsx
@@ -45259,7 +45259,11 @@
       <c r="D1281" t="n">
         <v>2238</v>
       </c>
-      <c r="E1281" t="inlineStr"/>
+      <c r="E1281" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
       <c r="F1281" t="n">
         <v>1280</v>
       </c>
@@ -45290,7 +45294,11 @@
       <c r="D1282" t="n">
         <v>2239</v>
       </c>
-      <c r="E1282" t="inlineStr"/>
+      <c r="E1282" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
       <c r="F1282" t="n">
         <v>1281</v>
       </c>
@@ -45356,7 +45364,11 @@
       <c r="D1284" t="n">
         <v>2243</v>
       </c>
-      <c r="E1284" t="inlineStr"/>
+      <c r="E1284" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
       <c r="F1284" t="n">
         <v>1283</v>
       </c>
@@ -51862,21 +51874,23 @@
       <c r="D1470" t="n">
         <v>2574</v>
       </c>
-      <c r="E1470" t="inlineStr"/>
+      <c r="E1470" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
       <c r="F1470" t="n">
         <v>1469</v>
       </c>
-      <c r="G1470" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
+      <c r="G1470" t="n">
+        <v>13.078219</v>
       </c>
       <c r="H1470" s="2" t="n">
         <v>45244.81056145292</v>
       </c>
       <c r="I1470" t="inlineStr">
         <is>
-          <t>Corrected: ResponseTime to NULL</t>
+          <t>Original</t>
         </is>
       </c>
     </row>
